--- a/internal_doc/05.测试设计/OM/数据操作/OM-数据操作（查询）-测试用例.xlsx
+++ b/internal_doc/05.测试设计/OM/数据操作/OM-数据操作（查询）-测试用例.xlsx
@@ -976,11 +976,11 @@
   <cols>
     <col min="1" max="1" width="31.625" style="1" customWidth="1"/>
     <col min="2" max="2" width="30" style="5" customWidth="1"/>
-    <col min="3" max="3" width="33.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="34.625" style="1" customWidth="1"/>
     <col min="4" max="6" width="5" style="1" customWidth="1"/>
     <col min="7" max="7" width="44.375" style="1" customWidth="1"/>
     <col min="8" max="8" width="34" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.875" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1056,7 +1056,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" s="4">
         <v>2</v>
@@ -1082,7 +1082,7 @@
         <v>2</v>
       </c>
       <c r="E4" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F4" s="4">
         <v>2</v>
@@ -1108,7 +1108,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" s="4">
         <v>2</v>
@@ -1134,7 +1134,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" s="4">
         <v>2</v>
@@ -1161,7 +1161,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" s="4">
         <v>2</v>
@@ -1187,7 +1187,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" s="4">
         <v>2</v>
@@ -1197,6 +1197,9 @@
       </c>
       <c r="H8" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="108">
@@ -1210,7 +1213,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" s="4">
         <v>2</v>
@@ -1220,6 +1223,9 @@
       </c>
       <c r="H9" s="2" t="s">
         <v>66</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="94.5">
@@ -1233,7 +1239,7 @@
         <v>2</v>
       </c>
       <c r="E10" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" s="4">
         <v>2</v>
@@ -1243,6 +1249,9 @@
       </c>
       <c r="H10" s="2" t="s">
         <v>62</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="94.5">
@@ -1256,7 +1265,7 @@
         <v>2</v>
       </c>
       <c r="E11" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11" s="4">
         <v>2</v>
@@ -1266,6 +1275,9 @@
       </c>
       <c r="H11" s="2" t="s">
         <v>61</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="108">
@@ -1279,7 +1291,7 @@
         <v>2</v>
       </c>
       <c r="E12" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="4">
         <v>2</v>
@@ -1289,6 +1301,9 @@
       </c>
       <c r="H12" s="2" t="s">
         <v>66</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="108">
@@ -1302,7 +1317,7 @@
         <v>2</v>
       </c>
       <c r="E13" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="4">
         <v>2</v>
@@ -1312,6 +1327,9 @@
       </c>
       <c r="H13" s="2" t="s">
         <v>62</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="108">
@@ -1325,7 +1343,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="4">
         <v>2</v>
@@ -1335,6 +1353,9 @@
       </c>
       <c r="H14" s="1" t="s">
         <v>71</v>
+      </c>
+      <c r="I14" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="94.5">
@@ -1348,7 +1369,7 @@
         <v>2</v>
       </c>
       <c r="E15" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="4">
         <v>2</v>
@@ -1358,6 +1379,9 @@
       </c>
       <c r="H15" s="1" t="s">
         <v>73</v>
+      </c>
+      <c r="I15" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="108">
@@ -1371,7 +1395,7 @@
         <v>2</v>
       </c>
       <c r="E16" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="4">
         <v>2</v>
@@ -1382,8 +1406,11 @@
       <c r="H16" s="1" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" ht="94.5">
+      <c r="I16" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="94.5">
       <c r="A17" s="5" t="s">
         <v>29</v>
       </c>
@@ -1394,7 +1421,7 @@
         <v>2</v>
       </c>
       <c r="E17" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="4">
         <v>2</v>
@@ -1405,8 +1432,11 @@
       <c r="H17" s="1" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" ht="81">
+      <c r="I17" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="81">
       <c r="A18" s="5" t="s">
         <v>18</v>
       </c>
@@ -1417,7 +1447,7 @@
         <v>2</v>
       </c>
       <c r="E18" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="4">
         <v>2</v>
@@ -1428,8 +1458,11 @@
       <c r="H18" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" ht="81">
+      <c r="I18" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="81">
       <c r="A19" s="5" t="s">
         <v>23</v>
       </c>
@@ -1440,7 +1473,7 @@
         <v>2</v>
       </c>
       <c r="E19" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="4">
         <v>2</v>
@@ -1451,8 +1484,11 @@
       <c r="H19" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="81">
+      <c r="I19" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="81">
       <c r="A20" s="5" t="s">
         <v>79</v>
       </c>
@@ -1463,7 +1499,7 @@
         <v>2</v>
       </c>
       <c r="E20" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F20" s="4">
         <v>2</v>
@@ -1474,8 +1510,11 @@
       <c r="H20" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" ht="81">
+      <c r="I20" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="81">
       <c r="A21" s="5" t="s">
         <v>80</v>
       </c>
@@ -1486,7 +1525,7 @@
         <v>2</v>
       </c>
       <c r="E21" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F21" s="4">
         <v>2</v>
@@ -1497,8 +1536,11 @@
       <c r="H21" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="81">
+      <c r="I21" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="81">
       <c r="A22" s="5" t="s">
         <v>81</v>
       </c>
@@ -1509,7 +1551,7 @@
         <v>2</v>
       </c>
       <c r="E22" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22" s="4">
         <v>2</v>
@@ -1520,8 +1562,11 @@
       <c r="H22" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="81">
+      <c r="I22" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="81">
       <c r="A23" s="5" t="s">
         <v>82</v>
       </c>
@@ -1532,7 +1577,7 @@
         <v>2</v>
       </c>
       <c r="E23" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" s="4">
         <v>2</v>
@@ -1543,8 +1588,11 @@
       <c r="H23" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" ht="81">
+      <c r="I23" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="81">
       <c r="A24" s="5" t="s">
         <v>78</v>
       </c>
@@ -1555,7 +1603,7 @@
         <v>2</v>
       </c>
       <c r="E24" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="4">
         <v>2</v>
@@ -1566,8 +1614,11 @@
       <c r="H24" s="1" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" ht="94.5">
+      <c r="I24" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="94.5">
       <c r="A25" s="5" t="s">
         <v>83</v>
       </c>
@@ -1578,7 +1629,7 @@
         <v>2</v>
       </c>
       <c r="E25" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="4">
         <v>2</v>
@@ -1588,6 +1639,9 @@
       </c>
       <c r="H25" s="2" t="s">
         <v>91</v>
+      </c>
+      <c r="I25" s="4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
